--- a/plantillas/40.xlsx
+++ b/plantillas/40.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cargue" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listas" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Productos" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="Cargue" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Listas" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="Productos" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="MARCA_1">Listas!$D$2:$D$2</definedName>
@@ -9215,7 +9215,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -9615,7 +9615,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -10653,7 +10653,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>24.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
     </row>

--- a/plantillas/40.xlsx
+++ b/plantillas/40.xlsx
@@ -9055,7 +9055,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -9795,7 +9795,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -10653,7 +10653,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>28.10.2026</t>
+          <t>29.10.2026</t>
         </is>
       </c>
     </row>

--- a/plantillas/40.xlsx
+++ b/plantillas/40.xlsx
@@ -9095,7 +9095,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -9795,7 +9795,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -10653,7 +10653,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>30.10.2026</t>
         </is>
       </c>
     </row>
